--- a/testing/REQUIREMENT_TRACEABILITY_MATRIX.xlsx
+++ b/testing/REQUIREMENT_TRACEABILITY_MATRIX.xlsx
@@ -463,16 +463,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1610,6 +1610,174 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-09</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Enforce legitimate email domain and syntax validation</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>FEAT-AUTH-01</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-009</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>test_email_legitimacy.png</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>BUG-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-10</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Mandatory 6-digit Email OTP verification via SMTP</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>FEAT-AUTH-01</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-010</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>test_otp_login_flow.png</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>BUG-007</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>REQ-STAT-01</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>New registered users initialize with zero streak/stats</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>FEAT-USER-01</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>TC-STAT-001</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>test_user_profile_load.png</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>BUG-006</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>REQ-E2E-01</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Selenium E2E automation verifies all core web journeys</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>FEAT-E2E-01</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEL-001</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Automated E2E</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>selenium_tests.log</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
